--- a/data/project_tracker.xlsx
+++ b/data/project_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81241728\Documents\PythonProjects\automation-project-tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED8729A-6969-4875-ABB1-B83A298F86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C439DB-88E5-4C76-819C-3EFB5FF71359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="366" yWindow="366" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2740" yWindow="-14510" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
   <si>
     <t>No</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Peru</t>
-  </si>
-  <si>
     <t>Brazil</t>
   </si>
   <si>
@@ -158,13 +155,19 @@
     <t>On going</t>
   </si>
   <si>
-    <t>Claims ROC</t>
-  </si>
-  <si>
     <t>Caribean</t>
   </si>
   <si>
     <t>Colombia</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Claims ROC Intake form</t>
+  </si>
+  <si>
+    <t>Listing Maintenance</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6.5234375" customWidth="1"/>
@@ -530,7 +533,7 @@
         <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -548,10 +551,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>8</v>
@@ -565,13 +568,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -616,7 +619,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -625,7 +628,7 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>120</v>
@@ -635,15 +638,15 @@
       </c>
       <c r="J3" s="2">
         <f>(G3*H3)/60</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2">
-        <f t="shared" ref="K3:K13" si="0">(G3*I3)/60</f>
-        <v>1.3333333333333333</v>
+        <f t="shared" ref="K3:K12" si="0">(G3*I3)/60</f>
+        <v>2</v>
       </c>
       <c r="L3" s="2">
         <f t="shared" ref="L3:L13" si="1">J3-K3</f>
-        <v>14.666666666666666</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" ref="M3:M13" si="2">L3/J3</f>
@@ -661,7 +664,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -706,7 +709,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -748,10 +751,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -793,10 +796,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -838,10 +841,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -883,10 +886,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -928,10 +931,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -970,19 +973,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -1015,19 +1018,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>12</v>
@@ -1060,13 +1063,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -1075,29 +1078,74 @@
         <v>16</v>
       </c>
       <c r="G13">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2">
         <f>(G13*H13)/60</f>
-        <v>125</v>
+        <v>116.66666666666667</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <f>(G13*I13)/60</f>
+        <v>11.666666666666666</v>
       </c>
       <c r="L13" s="2">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M13" s="3">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>52</v>
+      </c>
+      <c r="H14">
+        <v>15</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <f>(G14*H14)/60</f>
+        <v>13</v>
+      </c>
+      <c r="K14" s="2">
+        <f>(G14*I14)/60</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" ref="L14" si="4">J14-K14</f>
+        <v>13</v>
+      </c>
+      <c r="M14" s="3">
+        <f t="shared" ref="M14" si="5">L14/J14</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/project_tracker.xlsx
+++ b/data/project_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81241728\Documents\PythonProjects\automation-project-tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C439DB-88E5-4C76-819C-3EFB5FF71359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13111F65-B3AE-4290-8A89-EF45112DD060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2740" yWindow="-14510" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
   <si>
     <t>No</t>
   </si>
@@ -168,6 +168,18 @@
   </si>
   <si>
     <t>Listing Maintenance</t>
+  </si>
+  <si>
+    <t>Development time (hrs)</t>
+  </si>
+  <si>
+    <t>Capability Center</t>
+  </si>
+  <si>
+    <t>MCC</t>
+  </si>
+  <si>
+    <t>KCC</t>
   </si>
 </sst>
 </file>
@@ -505,24 +517,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6.5234375" customWidth="1"/>
     <col min="2" max="2" width="34.15625" customWidth="1"/>
-    <col min="3" max="3" width="9.7890625" customWidth="1"/>
-    <col min="4" max="4" width="13.83984375" customWidth="1"/>
-    <col min="6" max="6" width="11.62890625" customWidth="1"/>
-    <col min="7" max="7" width="17.68359375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.3125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.9453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.26171875" customWidth="1"/>
-    <col min="11" max="11" width="27" customWidth="1"/>
-    <col min="12" max="12" width="15.05078125" customWidth="1"/>
-    <col min="13" max="13" width="10.3671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7890625" customWidth="1"/>
+    <col min="5" max="5" width="13.83984375" customWidth="1"/>
+    <col min="7" max="8" width="11.62890625" customWidth="1"/>
+    <col min="9" max="9" width="17.68359375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.3125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.9453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.26171875" customWidth="1"/>
+    <col min="13" max="13" width="27" customWidth="1"/>
+    <col min="14" max="14" width="15.05078125" customWidth="1"/>
+    <col min="15" max="15" width="10.3671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,40 +543,46 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>1</v>
       </c>
@@ -571,44 +590,50 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="G2">
+      <c r="H2">
+        <v>90</v>
+      </c>
+      <c r="I2">
         <v>260</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>60</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>10</v>
       </c>
-      <c r="J2" s="2">
-        <f>(G2*H2)/60</f>
+      <c r="L2" s="2">
+        <f>(I2*J2)/60</f>
         <v>260</v>
       </c>
-      <c r="K2" s="2">
-        <f>(G2*I2)/60</f>
+      <c r="M2" s="2">
+        <f>(I2*K2)/60</f>
         <v>43.333333333333336</v>
       </c>
-      <c r="L2" s="2">
-        <f>J2-K2</f>
+      <c r="N2" s="2">
+        <f>L2-M2</f>
         <v>216.66666666666666</v>
       </c>
-      <c r="M2" s="3">
-        <f>L2/J2</f>
+      <c r="O2" s="3">
+        <f>N2/L2</f>
         <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2</v>
       </c>
@@ -616,44 +641,50 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="G3">
+      <c r="H3">
+        <v>70</v>
+      </c>
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>120</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="J3" s="2">
-        <f>(G3*H3)/60</f>
+      <c r="L3" s="2">
+        <f>(I3*J3)/60</f>
         <v>24</v>
       </c>
-      <c r="K3" s="2">
-        <f t="shared" ref="K3:K12" si="0">(G3*I3)/60</f>
+      <c r="M3" s="2">
+        <f t="shared" ref="M3:M12" si="0">(I3*K3)/60</f>
         <v>2</v>
       </c>
-      <c r="L3" s="2">
-        <f t="shared" ref="L3:L13" si="1">J3-K3</f>
+      <c r="N3" s="2">
+        <f t="shared" ref="N3:N13" si="1">L3-M3</f>
         <v>22</v>
       </c>
-      <c r="M3" s="3">
-        <f t="shared" ref="M3:M13" si="2">L3/J3</f>
+      <c r="O3" s="3">
+        <f t="shared" ref="O3:O13" si="2">N3/L3</f>
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>3</v>
       </c>
@@ -661,44 +692,50 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>16</v>
-      </c>
-      <c r="G4">
-        <v>260</v>
       </c>
       <c r="H4">
         <v>60</v>
       </c>
       <c r="I4">
+        <v>260</v>
+      </c>
+      <c r="J4">
+        <v>60</v>
+      </c>
+      <c r="K4">
         <v>0</v>
       </c>
-      <c r="J4" s="2">
-        <f>(G4*H4)/60</f>
+      <c r="L4" s="2">
+        <f>(I4*J4)/60</f>
         <v>260</v>
       </c>
-      <c r="K4" s="2">
+      <c r="M4" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="2">
+      <c r="N4" s="2">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
-      <c r="M4" s="3">
+      <c r="O4" s="3">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>4</v>
       </c>
@@ -706,44 +743,50 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>16</v>
       </c>
-      <c r="G5">
+      <c r="H5">
+        <v>24</v>
+      </c>
+      <c r="I5">
         <v>52</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>75</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>15</v>
       </c>
-      <c r="J5" s="2">
-        <f t="shared" ref="J5:J12" si="3">(G5*H5)/60</f>
+      <c r="L5" s="2">
+        <f t="shared" ref="L5:L12" si="3">(I5*J5)/60</f>
         <v>65</v>
       </c>
-      <c r="K5" s="2">
+      <c r="M5" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="L5" s="2">
+      <c r="N5" s="2">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="M5" s="3">
+      <c r="O5" s="3">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>5</v>
       </c>
@@ -751,44 +794,50 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
         <v>41</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="G6">
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>75</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="J6" s="2">
+      <c r="L6" s="2">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="K6" s="2">
+      <c r="M6" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L6" s="2">
+      <c r="N6" s="2">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="M6" s="3">
+      <c r="O6" s="3">
         <f t="shared" si="2"/>
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>6</v>
       </c>
@@ -796,44 +845,50 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="G7">
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>75</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="M7" s="3">
+      <c r="O7" s="3">
         <f t="shared" si="2"/>
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>7</v>
       </c>
@@ -841,44 +896,50 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
       <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
         <v>5</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="G8">
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8">
         <v>52</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>180</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>5</v>
       </c>
-      <c r="J8" s="2">
+      <c r="L8" s="2">
         <f t="shared" si="3"/>
         <v>156</v>
       </c>
-      <c r="K8" s="2">
+      <c r="M8" s="2">
         <f t="shared" si="0"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="L8" s="2">
+      <c r="N8" s="2">
         <f t="shared" si="1"/>
         <v>151.66666666666666</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <f t="shared" si="2"/>
         <v>0.97222222222222221</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>8</v>
       </c>
@@ -886,44 +947,50 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>16</v>
       </c>
-      <c r="G9">
+      <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>160</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>1</v>
       </c>
-      <c r="J9" s="2">
+      <c r="L9" s="2">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="K9" s="2">
+      <c r="M9" s="2">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="L9" s="2">
+      <c r="N9" s="2">
         <f t="shared" si="1"/>
         <v>31.8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <f t="shared" si="2"/>
         <v>0.99375000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>9</v>
       </c>
@@ -931,44 +998,50 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>35</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>16</v>
       </c>
-      <c r="G10">
+      <c r="H10">
+        <v>24</v>
+      </c>
+      <c r="I10">
         <v>52</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>20</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>1</v>
       </c>
-      <c r="J10" s="2">
+      <c r="L10" s="2">
         <f t="shared" si="3"/>
         <v>17.333333333333332</v>
       </c>
-      <c r="K10" s="2">
+      <c r="M10" s="2">
         <f t="shared" si="0"/>
         <v>0.8666666666666667</v>
       </c>
-      <c r="L10" s="2">
+      <c r="N10" s="2">
         <f t="shared" si="1"/>
         <v>16.466666666666665</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>10</v>
       </c>
@@ -976,44 +1049,50 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>20</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>31</v>
       </c>
-      <c r="G11">
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
         <v>6</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>600</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>1</v>
       </c>
-      <c r="J11" s="2">
+      <c r="L11" s="2">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="K11" s="2">
+      <c r="M11" s="2">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="L11" s="2">
+      <c r="N11" s="2">
         <f t="shared" si="1"/>
         <v>59.9</v>
       </c>
-      <c r="M11" s="3">
+      <c r="O11" s="3">
         <f t="shared" si="2"/>
         <v>0.99833333333333329</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1021,44 +1100,50 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>28</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>32</v>
       </c>
-      <c r="G12">
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
         <v>12</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>120</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>1</v>
       </c>
-      <c r="J12" s="2">
+      <c r="L12" s="2">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="K12" s="2">
+      <c r="M12" s="2">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="L12" s="2">
+      <c r="N12" s="2">
         <f t="shared" si="1"/>
         <v>23.8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <f t="shared" si="2"/>
         <v>0.9916666666666667</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1066,44 +1151,50 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>16</v>
       </c>
-      <c r="G13">
+      <c r="H13">
+        <v>15</v>
+      </c>
+      <c r="I13">
         <v>350</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>20</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>2</v>
       </c>
-      <c r="J13" s="2">
-        <f>(G13*H13)/60</f>
+      <c r="L13" s="2">
+        <f>(I13*J13)/60</f>
         <v>116.66666666666667</v>
       </c>
-      <c r="K13" s="2">
-        <f>(G13*I13)/60</f>
+      <c r="M13" s="2">
+        <f>(I13*K13)/60</f>
         <v>11.666666666666666</v>
       </c>
-      <c r="L13" s="2">
+      <c r="N13" s="2">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
-      <c r="M13" s="3">
+      <c r="O13" s="3">
         <f t="shared" si="2"/>
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1111,40 +1202,46 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>20</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>16</v>
       </c>
-      <c r="G14">
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
         <v>52</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>15</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>0</v>
       </c>
-      <c r="J14" s="2">
-        <f>(G14*H14)/60</f>
+      <c r="L14" s="2">
+        <f>(I14*J14)/60</f>
         <v>13</v>
       </c>
-      <c r="K14" s="2">
-        <f>(G14*I14)/60</f>
+      <c r="M14" s="2">
+        <f>(I14*K14)/60</f>
         <v>0</v>
       </c>
-      <c r="L14" s="2">
-        <f t="shared" ref="L14" si="4">J14-K14</f>
+      <c r="N14" s="2">
+        <f t="shared" ref="N14" si="4">L14-M14</f>
         <v>13</v>
       </c>
-      <c r="M14" s="3">
-        <f t="shared" ref="M14" si="5">L14/J14</f>
+      <c r="O14" s="3">
+        <f t="shared" ref="O14" si="5">N14/L14</f>
         <v>1</v>
       </c>
     </row>

--- a/data/project_tracker.xlsx
+++ b/data/project_tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81241728\Documents\PythonProjects\automation-project-tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13111F65-B3AE-4290-8A89-EF45112DD060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843F322B-B792-478F-B660-7B25CB27CDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2740" yWindow="-14510" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
   <si>
     <t>No</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>KCC</t>
+  </si>
+  <si>
+    <t>PepsiCo Browser SDK</t>
   </si>
 </sst>
 </file>
@@ -517,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6.5234375" customWidth="1"/>
@@ -1237,11 +1240,63 @@
         <v>0</v>
       </c>
       <c r="N14" s="2">
-        <f t="shared" ref="N14" si="4">L14-M14</f>
+        <f t="shared" ref="N14:N15" si="4">L14-M14</f>
         <v>13</v>
       </c>
       <c r="O14" s="3">
-        <f t="shared" ref="O14" si="5">N14/L14</f>
+        <f t="shared" ref="O14:O15" si="5">N14/L14</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15">
+        <v>45</v>
+      </c>
+      <c r="I15">
+        <f>260*3</f>
+        <v>780</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <f>(I15*J15)/60</f>
+        <v>65</v>
+      </c>
+      <c r="M15" s="2">
+        <f>(I15*K15)/60</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="4"/>
+        <v>65</v>
+      </c>
+      <c r="O15" s="3">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>

--- a/data/project_tracker.xlsx
+++ b/data/project_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81241728\Documents\PythonProjects\automation-project-tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843F322B-B792-478F-B660-7B25CB27CDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623BCC41-F773-40F9-8316-46C5126A2B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2740" yWindow="-14510" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="50">
   <si>
     <t>No</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>PepsiCo Browser SDK</t>
+  </si>
+  <si>
+    <t>Perfect Store EDF uploads</t>
   </si>
 </sst>
 </file>
@@ -520,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6.5234375" customWidth="1"/>
@@ -617,7 +620,7 @@
         <v>60</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2">
         <f>(I2*J2)/60</f>
@@ -625,15 +628,15 @@
       </c>
       <c r="M2" s="2">
         <f>(I2*K2)/60</f>
-        <v>43.333333333333336</v>
+        <v>21.666666666666668</v>
       </c>
       <c r="N2" s="2">
         <f>L2-M2</f>
-        <v>216.66666666666666</v>
+        <v>238.33333333333334</v>
       </c>
       <c r="O2" s="3">
         <f>N2/L2</f>
-        <v>0.83333333333333326</v>
+        <v>0.91666666666666674</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -668,7 +671,7 @@
         <v>120</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2">
         <f>(I3*J3)/60</f>
@@ -676,15 +679,15 @@
       </c>
       <c r="M3" s="2">
         <f t="shared" ref="M3:M12" si="0">(I3*K3)/60</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" s="2">
         <f t="shared" ref="N3:N13" si="1">L3-M3</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O3" s="3">
         <f t="shared" ref="O3:O13" si="2">N3/L3</f>
-        <v>0.91666666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -1298,6 +1301,57 @@
       <c r="O15" s="3">
         <f t="shared" si="5"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16">
+        <v>40</v>
+      </c>
+      <c r="I16">
+        <v>38</v>
+      </c>
+      <c r="J16">
+        <v>26</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16" s="2">
+        <f>(I16*J16)/60</f>
+        <v>16.466666666666665</v>
+      </c>
+      <c r="M16" s="2">
+        <f>(I16*K16)/60</f>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="N16" s="2">
+        <f t="shared" ref="N16" si="6">L16-M16</f>
+        <v>10.133333333333333</v>
+      </c>
+      <c r="O16" s="3">
+        <f t="shared" ref="O16" si="7">N16/L16</f>
+        <v>0.61538461538461542</v>
       </c>
     </row>
   </sheetData>
